--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487200_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487200_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. RUIZ ALCALA</t>
+          <t>P. ALBISU ASTIGARRAGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7003</v>
+        <v>1.6599</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2783</v>
+        <v>-0.9946</v>
       </c>
       <c r="F2" t="n">
-        <v>0.422</v>
+        <v>2.6545</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0353</v>
+        <v>2.3397</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4988</v>
+        <v>3.4486</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5341</v>
+        <v>-1.1089</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0621</v>
+        <v>3.3136</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0621</v>
+        <v>3.9897</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0.6762</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0268</v>
+        <v>-0.9739</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5609</v>
+        <v>-0.5411</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5341</v>
+        <v>-0.4327</v>
       </c>
       <c r="P2" t="n">
-        <v>0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-5.9833</v>
       </c>
       <c r="R2" t="n">
-        <v>0.965</v>
+        <v>3.0881</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7</v>
+        <v>0.0453</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2162</v>
+        <v>0.1613</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5162</v>
+        <v>-0.116</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2.1701</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5862</v>
+        <v>1.3731</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0986</v>
+        <v>1.698</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5123</v>
+        <v>-0.325</v>
       </c>
       <c r="G3" t="n">
         <v>0.7197</v>
@@ -688,13 +688,13 @@
         <v>0.965</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0945</v>
+        <v>-0.1186</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3107</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2162</v>
+        <v>-0.0288</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. LOPEZ BRETON</t>
+          <t>G. RUIZ ALCALA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6534</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.039</v>
+        <v>0.4772</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6925</v>
+        <v>0.4487</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9193</v>
+        <v>0.0353</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5134</v>
+        <v>-0.4988</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4326</v>
+        <v>0.5341</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0926</v>
+        <v>0.0621</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7088</v>
+        <v>0.0621</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3838</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1733</v>
+        <v>-0.0268</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2222</v>
+        <v>-0.5609</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0489</v>
+        <v>0.5341</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.0182</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2811</v>
+        <v>0.965</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0696</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9711</v>
+        <v>0.4151</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0984</v>
+        <v>-0.4895</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5983</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. ALBISU ASTIGARRAGA</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5048</v>
+        <v>-0.1117</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8552</v>
+        <v>-1.3614</v>
       </c>
       <c r="F5" t="n">
-        <v>2.36</v>
+        <v>1.2497</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3397</v>
+        <v>0.1585</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4486</v>
+        <v>0.9967</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1089</v>
+        <v>-0.8383</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3136</v>
+        <v>1.0793</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9897</v>
+        <v>1.6248</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6762</v>
+        <v>-0.5455</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9739</v>
+        <v>-0.9208</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5411</v>
+        <v>-0.628</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4327</v>
+        <v>-0.2928</v>
       </c>
       <c r="P5" t="n">
+        <v>-0.579</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-2.8951</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-5.9833</v>
-      </c>
       <c r="R5" t="n">
-        <v>3.0881</v>
+        <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1098</v>
+        <v>-0.3474</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6993</v>
+        <v>0.1686</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4105</v>
+        <v>-0.5159</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1701</v>
+        <v>0.6562</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6562</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>A. LOPEZ BRETON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1966</v>
+        <v>-0.6692</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5617</v>
+        <v>-2.2814</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7583</v>
+        <v>1.6121</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1585</v>
+        <v>1.9193</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9967</v>
+        <v>-0.5134</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8383</v>
+        <v>2.4326</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0793</v>
+        <v>2.0926</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6248</v>
+        <v>0.7088</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5455</v>
+        <v>1.3838</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9208</v>
+        <v>-0.1733</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.628</v>
+        <v>-1.2222</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2928</v>
+        <v>1.0489</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.579</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8951</v>
+        <v>-5.0182</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3161</v>
+        <v>3.2811</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.039</v>
+        <v>0.7469</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0317</v>
+        <v>0.7288</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0073</v>
+        <v>0.0181</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6562</v>
+        <v>-1.5983</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2859</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3704</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3438</v>
+        <v>-1.0434</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0284</v>
+        <v>-1.7279</v>
       </c>
       <c r="F7" t="n">
         <v>0.6846</v>
@@ -1000,10 +1000,10 @@
         <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5936</v>
+        <v>-0.2931</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.119</v>
+        <v>0.1814</v>
       </c>
       <c r="U7" t="n">
         <v>-0.4746</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7082</v>
+        <v>-1.1877</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3135</v>
+        <v>-0.9536</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3947</v>
+        <v>-0.2341</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3668</v>
@@ -1078,13 +1078,13 @@
         <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8276</v>
+        <v>-0.307</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6544</v>
+        <v>-0.2945</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1732</v>
+        <v>-0.0126</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2859</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8156</v>
+        <v>-1.3546</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.489</v>
+        <v>-2.1886</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6734</v>
+        <v>0.834</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0621</v>
@@ -1156,13 +1156,13 @@
         <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9465</v>
+        <v>-0.4855</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5354</v>
+        <v>-0.235</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4112</v>
+        <v>-0.2505</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0851</v>
+        <v>-2.5333</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6127</v>
+        <v>-3.7129</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5276</v>
+        <v>1.1796</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0633</v>
@@ -1234,13 +1234,13 @@
         <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5572</v>
+        <v>0.109</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0462</v>
+        <v>-0.1464</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6034</v>
+        <v>0.2554</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6576</v>
+        <v>-3.0439</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3541</v>
+        <v>-3.7939</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6965</v>
+        <v>0.7501</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1056</v>
@@ -1312,13 +1312,13 @@
         <v>2.5091</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.78</v>
+        <v>-0.1662</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4019</v>
+        <v>0.1583</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3781</v>
+        <v>-0.3246</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2314</v>
+        <v>-4.9181</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.3841</v>
+        <v>-7.1243</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1526</v>
+        <v>2.2061</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8486</v>
@@ -1390,13 +1390,13 @@
         <v>3.0881</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.156</v>
+        <v>0.1573</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2102</v>
+        <v>0.0496</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0542</v>
+        <v>0.1077</v>
       </c>
       <c r="V12" t="n">
         <v>1.5983</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.2004</v>
+        <v>-10.903</v>
       </c>
       <c r="E13" t="n">
-        <v>-22.2608</v>
+        <v>-21.9634</v>
       </c>
       <c r="F13" t="n">
-        <v>11.0605</v>
+        <v>11.0603</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8660999999999998</v>
@@ -1453,7 +1453,7 @@
         <v>-5.237</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.0468</v>
+        <v>-7.046799999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1.81</v>
@@ -1468,10 +1468,10 @@
         <v>21.2307</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0312</v>
+        <v>-0.7337</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7999000000000003</v>
+        <v>1.0973</v>
       </c>
       <c r="U13" t="n">
         <v>-1.8313</v>
@@ -1483,7 +1483,7 @@
         <v>4.4147</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.1023</v>
+        <v>-3.102300000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4435</v>
+        <v>6.859</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0611</v>
+        <v>2.2627</v>
       </c>
       <c r="F14" t="n">
-        <v>4.3825</v>
+        <v>4.5963</v>
       </c>
       <c r="G14" t="n">
         <v>4.0318</v>
@@ -1546,13 +1546,13 @@
         <v>5.7902</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6544</v>
+        <v>-0.2389</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4581</v>
+        <v>-0.2564</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1963</v>
+        <v>0.0175</v>
       </c>
       <c r="V14" t="n">
         <v>-0.794</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. HORCAJO GARCÍA</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3112</v>
+        <v>2.5013</v>
       </c>
       <c r="E15" t="n">
-        <v>1.046</v>
+        <v>-2.9237</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2651</v>
+        <v>5.4251</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.023</v>
+        <v>-0.2011</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3775</v>
+        <v>-0.3282</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3545</v>
+        <v>0.1271</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3374</v>
+        <v>0.2392</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3623</v>
+        <v>0.7604</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6998</v>
+        <v>-0.5212</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3604</v>
+        <v>-0.4403</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0152</v>
+        <v>-1.0886</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.6483</v>
       </c>
       <c r="P15" t="n">
-        <v>2.8951</v>
+        <v>0.386</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.965</v>
+        <v>-5.7902</v>
       </c>
       <c r="R15" t="n">
-        <v>3.8602</v>
+        <v>6.1763</v>
       </c>
       <c r="S15" t="n">
-        <v>1.667</v>
+        <v>0.4108</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6737</v>
+        <v>0.5417</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0066</v>
+        <v>-0.1309</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.228</v>
+        <v>1.9056</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.0856</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.228</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>J. HORCAJO GARCÍA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7753</v>
+        <v>2.4968</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.6233</v>
+        <v>0.0446</v>
       </c>
       <c r="F16" t="n">
-        <v>5.3986</v>
+        <v>2.4522</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2011</v>
+        <v>-0.023</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3282</v>
+        <v>-1.3775</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1271</v>
+        <v>1.3545</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2392</v>
+        <v>0.3374</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7604</v>
+        <v>-0.3623</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5212</v>
+        <v>0.6998</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4403</v>
+        <v>-0.3604</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0886</v>
+        <v>-1.0152</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6483</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.386</v>
+        <v>2.8951</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.7902</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>6.1763</v>
+        <v>3.8602</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6848</v>
+        <v>0.8527</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8421</v>
+        <v>0.6723</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1574</v>
+        <v>0.1804</v>
       </c>
       <c r="V16" t="n">
-        <v>1.9056</v>
+        <v>-1.228</v>
       </c>
       <c r="W16" t="n">
-        <v>2.0856</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.18</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MARTÍN CASTAÑEDA</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.401</v>
+        <v>2.2732</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6535</v>
+        <v>-0.9293</v>
       </c>
       <c r="F17" t="n">
-        <v>4.0545</v>
+        <v>3.2025</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.6084</v>
+        <v>-0.6857</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.5617</v>
+        <v>0.8073</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0468</v>
+        <v>-1.493</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.0749</v>
+        <v>-0.7993</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.448</v>
+        <v>1.749</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6269</v>
+        <v>-2.5483</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5336</v>
+        <v>0.1136</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1137</v>
+        <v>-0.9417</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4199</v>
+        <v>1.0553</v>
       </c>
       <c r="P17" t="n">
-        <v>3.4741</v>
+        <v>1.3511</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>4.4392</v>
+        <v>3.2811</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6511</v>
+        <v>0.274</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.2862</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2214</v>
+        <v>-0.0123</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8842</v>
+        <v>1.3339</v>
       </c>
       <c r="W17" t="n">
         <v>1.5138</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3704</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>A. MARTÍN CASTAÑEDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9668</v>
+        <v>2.2344</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5302</v>
+        <v>-1.9539</v>
       </c>
       <c r="F18" t="n">
-        <v>3.497</v>
+        <v>4.1884</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6857</v>
+        <v>-3.6084</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8073</v>
+        <v>-2.5617</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.493</v>
+        <v>-1.0468</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7993</v>
+        <v>-3.0749</v>
       </c>
       <c r="K18" t="n">
-        <v>1.749</v>
+        <v>-2.448</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.5483</v>
+        <v>-0.6269</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1136</v>
+        <v>-0.5336</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9417</v>
+        <v>-0.1137</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0553</v>
+        <v>-0.4199</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3511</v>
+        <v>3.4741</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>3.2811</v>
+        <v>4.4392</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0324</v>
+        <v>0.4845</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3146</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2822</v>
+        <v>-0.0876</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3339</v>
+        <v>1.8842</v>
       </c>
       <c r="W18" t="n">
         <v>1.5138</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.18</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9156</v>
+        <v>-1.7705</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6565</v>
+        <v>-3.4576</v>
       </c>
       <c r="F19" t="n">
-        <v>1.741</v>
+        <v>1.6871</v>
       </c>
       <c r="G19" t="n">
         <v>1.5262</v>
@@ -1936,13 +1936,13 @@
         <v>3.8602</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9578</v>
+        <v>0.1028</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9016</v>
+        <v>0.1005</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0562</v>
+        <v>0.0023</v>
       </c>
       <c r="V19" t="n">
         <v>-2.4345</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7819</v>
+        <v>-2.7263</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.704</v>
+        <v>-4.1031</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9221</v>
+        <v>1.3769</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1735</v>
@@ -2014,13 +2014,13 @@
         <v>4.4392</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2426</v>
+        <v>-0.187</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6861</v>
+        <v>-0.0852</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5566</v>
+        <v>-0.1018</v>
       </c>
       <c r="V20" t="n">
         <v>-1.9797</v>
@@ -2047,16 +2047,16 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>11.2003</v>
+        <v>11.8679</v>
       </c>
       <c r="E21" t="n">
-        <v>-11.0604</v>
+        <v>-11.0603</v>
       </c>
       <c r="F21" t="n">
-        <v>22.2608</v>
+        <v>22.9285</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8663000000000001</v>
+        <v>0.8662999999999998</v>
       </c>
       <c r="H21" t="n">
         <v>-0.5334000000000001</v>
@@ -2068,13 +2068,13 @@
         <v>5.2369</v>
       </c>
       <c r="K21" t="n">
-        <v>7.0469</v>
+        <v>7.046899999999999</v>
       </c>
       <c r="L21" t="n">
         <v>-1.8098</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.3707</v>
+        <v>-4.370699999999999</v>
       </c>
       <c r="N21" t="n">
         <v>-7.5802</v>
@@ -2092,13 +2092,13 @@
         <v>31.8464</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0313</v>
+        <v>1.6989</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8311</v>
+        <v>1.8312</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7998999999999999</v>
+        <v>-0.1324</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3125</v>
